--- a/daily_matches/job_matches_2026-09-16.xlsx
+++ b/daily_matches/job_matches_2026-09-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Senior Product Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, S3, Glue, Synapse, Data Lake, MLflow, Docker, Kubernetes, Apache Airflow</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a431ef26933c9cab</t>
+          <t>https://www.indeed.com/viewjob?jk=21a315f2df93550c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Dev Engineer SOW # EG CO1 B2 US</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22150a9313c85de5</t>
+          <t>https://www.indeed.com/viewjob?jk=d53cf9d0bf68048b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer-4</t>
+          <t>Python + Gen AI Developer - Dallas, TX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57517c8f22282773</t>
+          <t>https://www.indeed.com/viewjob?jk=68ca237f28e777e9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>Data Scientist, S3, BigQuery, Data Lake, AKS, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5cdad23779985</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb6bc702cc8f819</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Machine Learning &amp; AI</t>
+          <t>IT Site Reliability Engineer II - Data Platforms - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>UNFI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, XGBoost, LightGBM, MLflow, CI/CD, Snowflake</t>
+          <t>RAG, S3, Glue, Redshift, CI/CD, Terraform, Git, Databricks, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b89b1e56571ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8613083ecb455e28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Software Engineer, Solution Test-IQ Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Concord USA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL</t>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962688fb52f665fe</t>
+          <t>https://www.indeed.com/viewjob?jk=51b37e2194c538e3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Senior LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0520916947bccd63</t>
+          <t>https://www.indeed.com/viewjob?jk=1698a3db62a44dc8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Engineer - MLOps Platform(Remote Or Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e0d568c0fe3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=4815f622b7e398e4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b79178087231c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1fd9de87775b12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - GIPHY</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shutterstock</t>
+          <t>Corebridge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8a3ccea96eb16b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f307aa7663f4d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Python &amp; AI Engineer</t>
+          <t>AI Workflow Specialist Graduate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Tableau, Matplotlib, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d654bd73fb231c</t>
+          <t>https://www.indeed.com/viewjob?jk=fab040766fed1350</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>AI Engineer IV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Bates White Economic Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, MLflow, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70157732c8210316</t>
+          <t>https://www.indeed.com/viewjob?jk=93c43fecce5b4aa1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Forward Deployed AI/ML Engineer IV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Hadoop, PostgreSQL, MySQL</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Docker, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f86cdd4c675439</t>
+          <t>https://www.indeed.com/viewjob?jk=191a5d619c9740cd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>2027 Capital Markets, Quantitative Technology Services Summer Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788fc3c0ac9b4619</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb88e40dcb32f72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Engineer- Data/AI Focused</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, S3, Glue, Redshift, Data Lake, Redshift</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b320160e6257e21f</t>
+          <t>https://www.indeed.com/viewjob?jk=33e08a12c76721e4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Agent Developer, HR</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Git, Python, SQL, R</t>
+          <t>LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e070b3c5c1598076</t>
+          <t>https://www.indeed.com/viewjob?jk=c64076306656da4a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior GenAI/Python Engineer-4</t>
+          <t>Cloud Engineer - Full Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, Git, Snowflake</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b3ab5c94c4ff94</t>
+          <t>https://www.indeed.com/viewjob?jk=06271d579eb6e429</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Python Software Engineer III</t>
+          <t>Software Developer 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Stanford, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c215b809e214a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9639515e1e1da76</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52fb54968897c95b</t>
+          <t>https://www.indeed.com/viewjob?jk=d430b11f1930cc7f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Frontend Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>Newfold Digital</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka</t>
+          <t>LangChain, RAG, Gemini, FastAPI, CI/CD, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8c2d05083f261a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b69e226182f0dfd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-3</t>
+          <t>Backend Engineer - AI Platform and Cloud Native Services</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be4c7699606d282</t>
+          <t>https://www.indeed.com/viewjob?jk=b20ba90bb28e8931</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, RAG, MLflow, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c2403873b5face</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4bee6b245ec83d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Angi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,199 +1266,199 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642652601718b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a59827f5a55dfc2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Autonomous Learning Engineer</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d678656bb7f455</t>
+          <t>https://www.indeed.com/viewjob?jk=80232a361fb14257</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Multi-Asset Technology</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, Redshift, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f2956d380c932</t>
+          <t>https://www.indeed.com/viewjob?jk=da04a94127e9ea86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, CI/CD, Git, Python</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec7c86ea3dd6a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b54f1b4cf956f96e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bitsight</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422462ee0e6d8a60</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5665d035a226b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II- Eng</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1fc3f1de5d21dc</t>
+          <t>https://www.indeed.com/viewjob?jk=78fb922a9a3ab728</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-2</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e696b1edc4cf08e</t>
+          <t>https://www.indeed.com/viewjob?jk=b49bf30e82fb6005</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b484ed12c2b40287</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf9aff589670a0b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066727f04532303f</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e329db47d4f9b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ef5332e53acb34</t>
+          <t>https://www.indeed.com/viewjob?jk=cf61ddd926659796</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4627b81c811ec1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=547581c7398724b9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - AI, Agents, &amp; Context - Revenue Cycle (Associate)</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, Snowflake, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23e00d0574fce347</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1bb18cbd3b0584</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full-Stack &amp; AI Engineer</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NSPR Law Services LLC</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Santurce, PR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b207cf70bbbe1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad201c852f02231e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer- Multi-Asset Technology</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, Redshift, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d731490e4827974</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4883d8ca585d5f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364a81d63c9b4f89</t>
+          <t>https://www.indeed.com/viewjob?jk=249f6c30cadbbd34</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Senior Software Engineer (Fullstack CirrusMD)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
+          <t>Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94dece97872e5963</t>
+          <t>https://www.indeed.com/viewjob?jk=15354144589b885b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - August 2027</t>
+          <t>Software Engineering Internships, Summer 2027</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Inmar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718fa3c3e4a98b95</t>
+          <t>https://www.indeed.com/viewjob?jk=d641ee9fb89919a8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463e1932681d1ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=965baa9afcf09c70</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50e5db3bf7a0090</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb161b91790d71a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>SundaySky</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>Generative AI, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b7247de0da89be</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8b5f8dc0c286af</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Postdoctoral Fellow - Agentic AI Solutions and SciML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Pinecone, PyTorch, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d42517f4a6ea31f</t>
+          <t>https://www.indeed.com/viewjob?jk=493c6b39d5cf4d5c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Software Engineer – Manufacturing Digital Operations</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6deb5151a171c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c17d5756834ac8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Software Engineer – Enterprise Applications</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c9b376252505568</t>
+          <t>https://www.indeed.com/viewjob?jk=eaff489ad3919834</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Audiohook</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Eden, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>Data Scientist, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283361b16a1ebc55</t>
+          <t>https://www.indeed.com/viewjob?jk=2689d55ccffec09c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>KE Andrews</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Rockwall, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cbd383a79d4cbef</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fd0e71087c0abc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f223b258887bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=e42ab171a5adadb2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930899ea4c30eec</t>
+          <t>https://www.indeed.com/viewjob?jk=59a4ed0d2f4d671a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a609ef484a70728b</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe5183fd36ebb44</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d315fdda0e904f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8cae6aaaf59287</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63df87d110e211fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e92868a00965f116</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0e3854fb6006e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd81e04edc6a688</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269532a3a9e4d5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e1caafa30c2fb223</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd9ebe802598879</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2fbfa3c9248d88</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3579b3828b4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=09a9f0ed28f177eb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1cce3fa4d089a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4920f87b7e0a001c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cdfa4a99cf1b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=813d89a9da02cae3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3cd1e1f07261faf</t>
+          <t>https://www.indeed.com/viewjob?jk=5232e7d63e9c432f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de2979f66f2e58c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3c95dd71ae2003d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc4c1c460908c45</t>
+          <t>https://www.indeed.com/viewjob?jk=19a5d0d25c9fe547</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a881072cca7866f9</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3dab1a1182d31</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bc0d51ec16f366</t>
+          <t>https://www.indeed.com/viewjob?jk=60cd4c3487fc3db3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8840753fb3651a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=3755ebedccd82e72</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f63908830628ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=078e29f492d8c20e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06bbcb4a7c85812</t>
+          <t>https://www.indeed.com/viewjob?jk=db0523cb870d9518</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e1a7faad10c09b</t>
+          <t>https://www.indeed.com/viewjob?jk=b96dfe4eb5dc118b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5df440725468089</t>
+          <t>https://www.indeed.com/viewjob?jk=b545e0d12e2be729</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ebc749f6a1d990</t>
+          <t>https://www.indeed.com/viewjob?jk=db26e5fcac1a98e6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Ruby Developer - Project Software Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b631015d13883564</t>
+          <t>https://www.indeed.com/viewjob?jk=5c21381fbda81996</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Sr. Software Engineer Web Applications</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18dc70138cc32ac9</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bedf1d83553471</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Site Reliability Engineer - Fleet</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85824dce6929812</t>
+          <t>https://www.indeed.com/viewjob?jk=1883398fdda51060</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Site Reliability Engineer - Fleet</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd89770faca6190f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf583cdda8af216</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Platform Software Engineer, OCI Planning &amp; Capacity</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9109da232a7f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=bf5ac8eff18da1bc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enterprise AI Systems Engineer</t>
+          <t>AI Research Scientist III (Full Time) â€“ United States</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, AKS, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,637 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90542e98749e2837</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Enterprise AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>JUUL Labs</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, AKS, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba67ab5bc7e4a04</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Enterprise AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>JUUL Labs</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, AKS, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe935e70dd3f2e18</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Enterprise AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>JUUL Labs</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, AKS, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=037741e66967443c</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>CG Infinity</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Redshift, Git, Snowflake, Redshift, Tableau, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06d6e56ef7c81de</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>AI Solutions Software Engineer II/III</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Firefly Aerospace</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Cedar Park, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa6f8c71f5d93bf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer (Full Stack) - Agent Factory</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab774b0dd273cb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Analyst, Production Support</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Expion health</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>S3, CI/CD, Git, Snowflake, MySQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=249f623fa05a779f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Centene</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>S3, Glue, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b48caf12e9a2d919</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior DevOps/SRE Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>CREDIT GENIE</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=185bf275b710bed6</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Embedded Software Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RAG, Cortex, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49e3ad470f341624</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Design Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Eastman Chemical</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Kingsport, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8969d088d003fe99</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>AI Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Phoenix Business Consulting</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Northborough, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44cdf29df159e75d</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Cloud Ops Engineer II (Remote)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Signet Jewelers</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Coppell, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d73f7d9acbb1fb21</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>AI First Engineer – SCM Planning</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1adbac1760d39612</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>CentralReach</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3feec8ed9613b9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>CentralReach</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Holmdel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa17361991faf898</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Software Engineer Associate</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Freddie Mac</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89f34c959540154c</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>AI Red Team Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>White Circle</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Mistral, AKS, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb05645b1ef4495</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f14bf01e457da2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-16.xlsx
+++ b/daily_matches/job_matches_2026-09-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Sr. AI/Python Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, MLflow, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b2c0563ecfc04e</t>
+          <t>https://www.indeed.com/viewjob?jk=2668edd7349e606b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Veson Nautical</t>
+          <t>ebbo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, Terraform, Git, BigQuery, PostgreSQL</t>
+          <t>RAG, Copilot, S3, Apache Airflow, CI/CD, Terraform, Git, Snowflake, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c626e90462e462c</t>
+          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Early Career AI Engineer (Contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rakuten Global</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Git, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, RAG, Data Lake, Terraform, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfbeb39447839e</t>
+          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Marketing Measurement, Consumer Solutions</t>
+          <t>Sr Data Scientist - AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f107d0ed30e894c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b27957a130be09b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Inperson Interview_AI SDET_NY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Databricks, Python</t>
+          <t>RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd21fd4293097f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=67b2be96a3959509</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Platform Automation Engineer - USA Remote</t>
+          <t>Stardog Admin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Databricks, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,207 +671,207 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a756a5b4f72f8f56</t>
+          <t>https://www.indeed.com/viewjob?jk=13a16d396aacef30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Platform Infrastructure Engineer, AI Transformation</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Synapse, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6607306b59d3e34c</t>
+          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FS Engineer</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Sinch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, CI/CD, Git, Databricks, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, Terraform, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dce7ee1a41b7442</t>
+          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Hadoop, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, S3, Glue, Athena, Kinesis, Git, Snowflake, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d260e41a66c285a8</t>
+          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, AI Agents &amp; Automation</t>
+          <t>Machine Learning Engineer, Jr.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Wings Credit Union</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Databricks, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c505906ec4e1832c</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef3652ae012e98</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stardog Admin/DevOps Consultant</t>
+          <t>Infrastructure Engineer - Edge AI Platform - Qualcomm - Remote - Europe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Databricks, PostgreSQL, SQL, R, Scala</t>
+          <t>S3, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a91e2ec93b2c129</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5201c47e04bd48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist, Ricochet Anti-Cheat (Call of Duty)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Avaloq</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sherman Oaks, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, AKS, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21276df397099f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=07598abcce4e29da</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Database Reliability Engineer</t>
+          <t>Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, Kafka, PostgreSQL, MySQL, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, Databricks, PySpark, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,707 +916,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccccc3493829df1e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7655c25283dd63</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b1680d51ee7650</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Full Stack .NET Developer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=751e2004c7895ad9</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Smart Manufacturing and Automation Intern</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6353145d88aab0b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Test (Org Modeling)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c220e6d2170d0e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Automation QA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Databricks, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ffd4fd4d17a66c</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AI-Native Software Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, CI/CD, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25eb777743ca25</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI-Native Software Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, CI/CD, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e97200c7fc4c35e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI-Native Software Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, CI/CD, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c586e8f2f1ee600</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI-Native Software Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bedminster, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, CI/CD, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7219b7f3e61f8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Guidewire</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=315b9b89e3893208</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=180e2e1d120eeb3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Avaloq</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a40b37c6bb56b89</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Smart Apply Test Company</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed67ef591c83666</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Logic, Inc.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f592362715244417</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Cox Automotive</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Carmel, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c06a4bf8bf5eacf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Java - Neovest</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Pleasant Grove, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=218a739110e2edc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Architect, Senior - AI Cost Optimization</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Infor</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1338609b3f59bfb</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AI &amp; Data Engineering Consultant</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=818d084cd4d9432e</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software Engineer III (AI)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Novant Health</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, PySpark, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=816396425bf9de25</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Database Administrator - PostgreSQL Carmel, United States Sep. 15, 2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Alter Domus</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Carmel, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=466ef9cc01d7f367</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b35fdb354c89df</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-16.xlsx
+++ b/daily_matches/job_matches_2026-09-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI/Python Engineer</t>
+          <t>Senior Calypso Java Developer Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Tekserv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, MLflow, FastAPI, Docker, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2668edd7349e606b</t>
+          <t>https://www.indeed.com/viewjob?jk=8359a4f919eb2d99</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer (Breakthrough)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ebbo</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Apache Airflow, CI/CD, Terraform, Git, Snowflake, PostgreSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, TensorFlow, BigQuery, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00129c0be2bb43b6</t>
+          <t>https://www.indeed.com/viewjob?jk=270c40cce30d61aa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist &amp; Machine Learning Engineer (Bellevue, Denver or LA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Identity Digital</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Terraform, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, MLflow, Kubernetes, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6629a97b773e9046</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c697474cdd2518</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, Apache Airflow, CI/CD, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b27957a130be09b</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1559bf7f9b420</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Inperson Interview_AI SDET_NY</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b2be96a3959509</t>
+          <t>https://www.indeed.com/viewjob?jk=aec8c83533c1022a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Stardog Admin</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Databricks, PostgreSQL, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a16d396aacef30</t>
+          <t>https://www.indeed.com/viewjob?jk=809c4a570b350ca6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>National Computer Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Synapse, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Data Lake, MLflow, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3504f95af705a178</t>
+          <t>https://www.indeed.com/viewjob?jk=91ce31f9ba1d4192</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Senior Software Engineer - AI, Agentic Applications, Enterprise Integration</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sinch</t>
+          <t>Ashurst Perkins Coie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc06fce927a41534</t>
+          <t>https://www.indeed.com/viewjob?jk=e4acf2ce05267bef</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Athena, Kinesis, Git, Snowflake, NoSQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, CI/CD, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e8077574f9d2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=4f897bb19ef28f37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Jr.</t>
+          <t>DevOps Engineer – GitHub Actions &amp; Jenkins</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wings Credit Union</t>
+          <t>NxtPods</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Databricks, Tableau, Python, SQL, R, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef3652ae012e98</t>
+          <t>https://www.indeed.com/viewjob?jk=72383824393bdf97</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer - Edge AI Platform - Qualcomm - Remote - Europe</t>
+          <t>Data Scientist, Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5201c47e04bd48</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6010a7c6692353</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Avaloq</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07598abcce4e29da</t>
+          <t>https://www.indeed.com/viewjob?jk=4e7197ad026e98ea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - Remote</t>
+          <t>Senior Engineer, DevOps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Databricks, PySpark, Python, R, Optimization</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,1932 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7655c25283dd63</t>
+          <t>https://www.indeed.com/viewjob?jk=32de19c35f30429d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Developer Productivity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7d2f03370017a2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vusion</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=735050e479c00968</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Forward Deployed Data Engineer IV, Databricks</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, CI/CD, Git, Databricks, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=627e4c76bb2cd649</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Full-Stack Java Developer / Consultant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Keyhole Software</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lenexa, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be2787b7c178dd55</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aligned Data Centers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Kinesis, CI/CD, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da2322fc8a33bd97</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning &amp; Computer Vision Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Molecular Devices</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c9e46edb61700e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Forward Deployed Data Engineer IV, Databricks</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, CI/CD, Git, Databricks, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4722cbd707f902fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, Kafka, Dask, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9beae62bd7c3a68d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer IV, Payment Platform</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Toshiba Global Commerce Solutions</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d93b3ef61ed7a69</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Federal AI Self-Paced Instructor/SME (Contract)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Graduate School USA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Power BI, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dcca92157d9dbc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer (Entry level - Remote US)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76bbd1aa819d5c43</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist - Telecommute</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Plymouth, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a70080fde0a0443b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer III - Network Perimeter &amp; CDN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e897f961b1279f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc3fa737c3d8b9ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI FinOps Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ca21d1e0fd3076a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software DevOps Engineer, Networking</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc4ef0b9b165ee11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef4a72b86d37bff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00a98a2d8c15d1a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e8181787c8461d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mindbody</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ac3490fba89c516</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer II Full Stack (Java/Node.js/Angular)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Western Governors University</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Athena, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=208d2d30706a39b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA Engineer Associate</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Delta Dental</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab2b1623c4138b2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Azure Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wachter</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lenexa, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=615680cce8224f90</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f93b157e11d95dc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c454fd78424de2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38be6473ee964359</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=526d8031fd6e0b16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b02b195ca79ab9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a68f8daa124364f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b75a24a7b8930e93</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr. Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0100902a8f5b921b</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff4f1a06d643af2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8f3452b221a96e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1fc6b2cba00f841</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ce8569dd440dffc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fd464441af4f7f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e4145f82a9a669c</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b35fdb354c89df</t>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11a2979f62ecbda8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04065616279d9f9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5060a8562d304082</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2de34a831a93e737</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bae8773fee4eced6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=251e992e4eba6505</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65794d0e56f36d70</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bbac9f592327e2f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2604709e969bbc7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a900df1052eb8e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f0d1197d2f3a0e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe5b8f016c9e8a9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Culver City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63d62a4b41973b58</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b57bda8e8a9dfbee</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a9177d3a32dc219</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AI Led Forward Deployed Engineer | Design &amp; Digital Products</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0e20be94f0625e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior - Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e78f3363e5dc369</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Desktop Software Engineer &amp; Application Modernization</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Lawrence J. Berger, PC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2563d99708404214</t>
         </is>
       </c>
     </row>
